--- a/agents/compassus-capacity-pm/variables/CapacitySchedulingVariableWorkbook.xlsx
+++ b/agents/compassus-capacity-pm/variables/CapacitySchedulingVariableWorkbook.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>87 variables from the 19 Aug inventory, plus 1 flagged gap. Nothing dropped.</t>
+          <t>93 variables: the 76 numbered rows from the 8.13 inventory, the 3 it carried without IDs, and 14 added since. Nothing dropped.</t>
         </is>
       </c>
       <c r="D30" s="12">
@@ -1583,7 +1583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U94"/>
+  <dimension ref="A1:AD94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1607,6 +1607,15 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="62" customWidth="1" min="20" max="20"/>
     <col width="44" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1715,6 +1724,51 @@
           <t>Open question for the team</t>
         </is>
       </c>
+      <c r="V1" s="15" t="inlineStr">
+        <is>
+          <t>Constraint (8.13)</t>
+        </is>
+      </c>
+      <c r="W1" s="15" t="inlineStr">
+        <is>
+          <t>Sourced by (8.13)</t>
+        </is>
+      </c>
+      <c r="X1" s="15" t="inlineStr">
+        <is>
+          <t>Current state (8.13)</t>
+        </is>
+      </c>
+      <c r="Y1" s="15" t="inlineStr">
+        <is>
+          <t>Source of truth (8.13)</t>
+        </is>
+      </c>
+      <c r="Z1" s="15" t="inlineStr">
+        <is>
+          <t>Measurability (8.13)</t>
+        </is>
+      </c>
+      <c r="AA1" s="15" t="inlineStr">
+        <is>
+          <t>Automation confidence (8.13)</t>
+        </is>
+      </c>
+      <c r="AB1" s="15" t="inlineStr">
+        <is>
+          <t>Rollup key (8.13)</t>
+        </is>
+      </c>
+      <c r="AC1" s="15" t="inlineStr">
+        <is>
+          <t>Weight (8.13)</t>
+        </is>
+      </c>
+      <c r="AD1" s="15" t="inlineStr">
+        <is>
+          <t>Conflict risk (8.13)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="76" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
@@ -1822,6 +1876,49 @@
           <t>Which system wins when Workday and HCHB disagree on who is active?</t>
         </is>
       </c>
+      <c r="V2" s="16" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="W2" s="16" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="X2" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y2" s="16" t="inlineStr">
+        <is>
+          <t>Workday + HCHB</t>
+        </is>
+      </c>
+      <c r="Z2" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA2" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB2" s="16" t="inlineStr">
+        <is>
+          <t>SHD-A</t>
+        </is>
+      </c>
+      <c r="AC2" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD2" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="76" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
@@ -1929,6 +2026,49 @@
           <t>Are the discipline codes identical in Workday and HCHB, or do they need mapping?</t>
         </is>
       </c>
+      <c r="V3" s="16" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="W3" s="16" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="X3" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y3" s="16" t="inlineStr">
+        <is>
+          <t>Workday + HCHB</t>
+        </is>
+      </c>
+      <c r="Z3" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA3" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB3" s="16" t="inlineStr">
+        <is>
+          <t>SHD-A</t>
+        </is>
+      </c>
+      <c r="AC3" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="76" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
@@ -2036,6 +2176,49 @@
           <t>Is the assessing/assistant split written down as policy anywhere, or only understood?</t>
         </is>
       </c>
+      <c r="V4" s="16" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="W4" s="16" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="X4" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y4" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="Z4" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA4" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB4" s="16" t="inlineStr">
+        <is>
+          <t>SHD-A</t>
+        </is>
+      </c>
+      <c r="AC4" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD4" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="76" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
@@ -2139,6 +2322,49 @@
           <t>Do per-diem and contract clinicians carry an FTE value at all, or are they null?</t>
         </is>
       </c>
+      <c r="V5" s="16" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="W5" s="16" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="X5" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y5" s="16" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="Z5" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA5" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB5" s="16" t="inlineStr">
+        <is>
+          <t>SHD-A</t>
+        </is>
+      </c>
+      <c r="AC5" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD5" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="76" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
@@ -2242,6 +2468,49 @@
           <t>Who owns the branch roll-up today — is anyone producing this view at all?</t>
         </is>
       </c>
+      <c r="V6" s="16" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="W6" s="16" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="X6" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y6" s="16" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="Z6" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA6" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB6" s="16" t="inlineStr">
+        <is>
+          <t>CAP-A</t>
+        </is>
+      </c>
+      <c r="AC6" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD6" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="76" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
@@ -2349,6 +2618,49 @@
           <t>Is there a maintained per-diem availability list anywhere, or is it rebuilt from memory each time?</t>
         </is>
       </c>
+      <c r="V7" s="16" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="W7" s="16" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="X7" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Y7" s="16" t="inlineStr">
+        <is>
+          <t>Manual + HCHB</t>
+        </is>
+      </c>
+      <c r="Z7" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA7" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB7" s="16" t="inlineStr">
+        <is>
+          <t>CAP-E</t>
+        </is>
+      </c>
+      <c r="AC7" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD7" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="76" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
@@ -2456,6 +2768,49 @@
           <t>Is there a competency list per clinician anywhere today, and who would own keeping it current?</t>
         </is>
       </c>
+      <c r="V8" s="16" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="W8" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X8" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y8" s="16" t="inlineStr">
+        <is>
+          <t>Workday + Manual</t>
+        </is>
+      </c>
+      <c r="Z8" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA8" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB8" s="16" t="inlineStr">
+        <is>
+          <t>CAP-F</t>
+        </is>
+      </c>
+      <c r="AC8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
@@ -2559,6 +2914,49 @@
           <t>Is there a standard ramp expectation by discipline, or is it manager-by-manager?</t>
         </is>
       </c>
+      <c r="V9" s="16" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="W9" s="16" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="X9" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y9" s="16" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="Z9" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA9" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB9" s="16" t="inlineStr">
+        <is>
+          <t>CAP-G</t>
+        </is>
+      </c>
+      <c r="AC9" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="76" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
@@ -2666,6 +3064,49 @@
           <t>Is the rotation kept in HCHB, or on a separate branch calendar?</t>
         </is>
       </c>
+      <c r="V10" s="16" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="W10" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X10" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y10" s="16" t="inlineStr">
+        <is>
+          <t>HCHB</t>
+        </is>
+      </c>
+      <c r="Z10" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA10" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB10" s="16" t="inlineStr">
+        <is>
+          <t>CAP-C</t>
+        </is>
+      </c>
+      <c r="AC10" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="76" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
@@ -2773,6 +3214,49 @@
           <t>Would clinicians accept this being visible at all? This is a trust question before it is a data question.</t>
         </is>
       </c>
+      <c r="V11" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W11" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X11" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y11" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z11" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA11" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB11" s="16" t="inlineStr">
+        <is>
+          <t>SCH-C</t>
+        </is>
+      </c>
+      <c r="AC11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="76" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
@@ -2880,6 +3364,49 @@
           <t>If we attach an incentive to hard-to-fill visits, who sets it and who approves the spend?</t>
         </is>
       </c>
+      <c r="V12" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W12" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X12" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y12" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z12" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA12" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB12" s="16" t="inlineStr">
+        <is>
+          <t>SCH-C</t>
+        </is>
+      </c>
+      <c r="AC12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="76" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
@@ -2987,6 +3514,49 @@
           <t>What would it take to turn the Workday-to-HCHB availability integration back on?</t>
         </is>
       </c>
+      <c r="V13" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W13" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X13" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y13" s="16" t="inlineStr">
+        <is>
+          <t>Workday + HCHB</t>
+        </is>
+      </c>
+      <c r="Z13" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA13" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB13" s="16" t="inlineStr">
+        <is>
+          <t>SHD-B</t>
+        </is>
+      </c>
+      <c r="AC13" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD13" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="76" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
@@ -3094,6 +3664,49 @@
           <t>Is the current zip-to-clinician assignment complete in HCHB, or does the scheduler hold part of it?</t>
         </is>
       </c>
+      <c r="V14" s="16" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="W14" s="16" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="X14" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Y14" s="16" t="inlineStr">
+        <is>
+          <t>HCHB + Manual + Census</t>
+        </is>
+      </c>
+      <c r="Z14" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA14" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB14" s="16" t="inlineStr">
+        <is>
+          <t>SHD-C</t>
+        </is>
+      </c>
+      <c r="AC14" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD14" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="76" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
@@ -3197,6 +3810,49 @@
           <t>Does the recorded coverage area match what the branch actually accepts in practice?</t>
         </is>
       </c>
+      <c r="V15" s="16" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="W15" s="16" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="X15" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y15" s="16" t="inlineStr">
+        <is>
+          <t>HCHB</t>
+        </is>
+      </c>
+      <c r="Z15" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA15" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB15" s="16" t="inlineStr">
+        <is>
+          <t>CAP-B</t>
+        </is>
+      </c>
+      <c r="AC15" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD15" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="76" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
@@ -3304,6 +3960,49 @@
           <t>How current is the zip assignment in HCHB right now — and when was it last reviewed against referral patterns?</t>
         </is>
       </c>
+      <c r="V16" s="16" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="W16" s="16" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="X16" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Y16" s="16" t="inlineStr">
+        <is>
+          <t>HCHB + Manual</t>
+        </is>
+      </c>
+      <c r="Z16" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA16" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB16" s="16" t="inlineStr">
+        <is>
+          <t>CAP-B</t>
+        </is>
+      </c>
+      <c r="AC16" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD16" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="76" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
@@ -3407,6 +4106,49 @@
           <t>Do we want to make this call before vendor selection, or let the shortlist show us what is practical?</t>
         </is>
       </c>
+      <c r="V17" s="16" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="W17" s="16" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="X17" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y17" s="16" t="inlineStr">
+        <is>
+          <t>Census</t>
+        </is>
+      </c>
+      <c r="Z17" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA17" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB17" s="16" t="inlineStr">
+        <is>
+          <t>CAP-B</t>
+        </is>
+      </c>
+      <c r="AC17" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD17" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
@@ -3514,6 +4256,15 @@
           <t>What cadence do we want for territory review, and who convenes it?</t>
         </is>
       </c>
+      <c r="V18" s="16" t="n"/>
+      <c r="W18" s="16" t="n"/>
+      <c r="X18" s="16" t="n"/>
+      <c r="Y18" s="16" t="n"/>
+      <c r="Z18" s="16" t="n"/>
+      <c r="AA18" s="16" t="n"/>
+      <c r="AB18" s="16" t="n"/>
+      <c r="AC18" s="16" t="n"/>
+      <c r="AD18" s="16" t="n"/>
     </row>
     <row r="19" ht="76" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
@@ -3621,6 +4372,15 @@
           <t>Who asks, and how often? This only works if the answer is collected rather than derived.</t>
         </is>
       </c>
+      <c r="V19" s="16" t="n"/>
+      <c r="W19" s="16" t="n"/>
+      <c r="X19" s="16" t="n"/>
+      <c r="Y19" s="16" t="n"/>
+      <c r="Z19" s="16" t="n"/>
+      <c r="AA19" s="16" t="n"/>
+      <c r="AB19" s="16" t="n"/>
+      <c r="AC19" s="16" t="n"/>
+      <c r="AD19" s="16" t="n"/>
     </row>
     <row r="20" ht="76" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
@@ -3728,6 +4488,49 @@
           <t>Confirm which HCHB view the branch actually uses for committed points, and whether pending-auth visits appear anywhere in it.</t>
         </is>
       </c>
+      <c r="V20" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="W20" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X20" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y20" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="Z20" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA20" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB20" s="16" t="inlineStr">
+        <is>
+          <t>CAP-C</t>
+        </is>
+      </c>
+      <c r="AC20" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="76" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
@@ -3835,6 +4638,49 @@
           <t>Does any current HCHB view show open points by day, or is this genuinely net-new?</t>
         </is>
       </c>
+      <c r="V21" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="W21" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X21" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y21" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="Z21" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA21" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB21" s="16" t="inlineStr">
+        <is>
+          <t>CAP-D</t>
+        </is>
+      </c>
+      <c r="AC21" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="76" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
@@ -3938,6 +4784,49 @@
           <t>What is the decision this number should drive, and who makes it — ED, DCS, or intake?</t>
         </is>
       </c>
+      <c r="V22" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="W22" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X22" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y22" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="Z22" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA22" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB22" s="16" t="inlineStr">
+        <is>
+          <t>CAP-D</t>
+        </is>
+      </c>
+      <c r="AC22" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD22" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="76" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
@@ -4045,6 +4934,49 @@
           <t>How does the branch decide today whether it can take another admission — what is the current proxy?</t>
         </is>
       </c>
+      <c r="V23" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="W23" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X23" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y23" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="Z23" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA23" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB23" s="16" t="inlineStr">
+        <is>
+          <t>CAP-D</t>
+        </is>
+      </c>
+      <c r="AC23" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD23" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="76" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
@@ -4152,6 +5084,49 @@
           <t>Open question #1: do points account for travel, documentation and acuity, or only visit type?</t>
         </is>
       </c>
+      <c r="V24" s="16" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="W24" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X24" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y24" s="16" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="Z24" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA24" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB24" s="16" t="inlineStr">
+        <is>
+          <t>SHD-D</t>
+        </is>
+      </c>
+      <c r="AC24" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD24" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="76" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
@@ -4255,6 +5230,49 @@
           <t>Are targets uniform across branches and disciplines, or do they vary?</t>
         </is>
       </c>
+      <c r="V25" s="16" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="W25" s="16" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="X25" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y25" s="16" t="inlineStr">
+        <is>
+          <t>HCHB + Config</t>
+        </is>
+      </c>
+      <c r="Z25" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA25" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB25" s="16" t="inlineStr">
+        <is>
+          <t>SHD-E</t>
+        </is>
+      </c>
+      <c r="AC25" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD25" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="76" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
@@ -4362,6 +5380,49 @@
           <t>Is discharge date reliable enough in HCHB to forecast returning capacity?</t>
         </is>
       </c>
+      <c r="V26" s="16" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="W26" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X26" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y26" s="16" t="inlineStr">
+        <is>
+          <t>HCHB</t>
+        </is>
+      </c>
+      <c r="Z26" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA26" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB26" s="16" t="inlineStr">
+        <is>
+          <t>SHD-F</t>
+        </is>
+      </c>
+      <c r="AC26" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD26" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="76" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
@@ -4465,6 +5526,49 @@
           <t>Confirm this stays out of scope as the initiative moves into future-state design.</t>
         </is>
       </c>
+      <c r="V27" s="16" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="W27" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X27" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y27" s="16" t="inlineStr">
+        <is>
+          <t>HCHB</t>
+        </is>
+      </c>
+      <c r="Z27" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA27" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB27" s="16" t="inlineStr">
+        <is>
+          <t>CAP-H</t>
+        </is>
+      </c>
+      <c r="AC27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="76" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
@@ -4572,6 +5676,49 @@
           <t>Are working patterns recorded in HCHB per clinician, or reconstructed by the scheduler each week?</t>
         </is>
       </c>
+      <c r="V28" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W28" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X28" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y28" s="16" t="inlineStr">
+        <is>
+          <t>Manual + HCHB</t>
+        </is>
+      </c>
+      <c r="Z28" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA28" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB28" s="16" t="inlineStr">
+        <is>
+          <t>SCH-C</t>
+        </is>
+      </c>
+      <c r="AC28" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="76" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
@@ -4675,6 +5822,49 @@
           <t>Do we want to set a branch expectation on first-visit time, or keep it individual?</t>
         </is>
       </c>
+      <c r="V29" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W29" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X29" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y29" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z29" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA29" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB29" s="16" t="inlineStr">
+        <is>
+          <t>SCH-C</t>
+        </is>
+      </c>
+      <c r="AC29" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="76" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
@@ -4778,6 +5968,49 @@
           <t>None — this row is intentionally read-only.</t>
         </is>
       </c>
+      <c r="V30" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W30" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X30" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y30" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z30" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA30" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB30" s="16" t="inlineStr">
+        <is>
+          <t>SCH-C</t>
+        </is>
+      </c>
+      <c r="AC30" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="76" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
@@ -4881,6 +6114,49 @@
           <t>Would clinicians be willing to record this, or does it feel like surveillance?</t>
         </is>
       </c>
+      <c r="V31" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W31" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X31" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y31" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z31" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA31" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB31" s="16" t="inlineStr">
+        <is>
+          <t>SCH-C</t>
+        </is>
+      </c>
+      <c r="AC31" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="76" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
@@ -4984,6 +6260,49 @@
           <t>Should documentation time be represented in the point system? Ties to open question #1.</t>
         </is>
       </c>
+      <c r="V32" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W32" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X32" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y32" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z32" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA32" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB32" s="16" t="inlineStr">
+        <is>
+          <t>SCH-C</t>
+        </is>
+      </c>
+      <c r="AC32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="76" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
@@ -5087,6 +6406,49 @@
           <t>None — intentionally read-only.</t>
         </is>
       </c>
+      <c r="V33" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W33" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X33" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y33" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z33" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA33" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB33" s="16" t="inlineStr">
+        <is>
+          <t>SCH-C</t>
+        </is>
+      </c>
+      <c r="AC33" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD33" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="76" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
@@ -5190,6 +6552,49 @@
           <t>Is there a place a clinician could record a standing hard stop today?</t>
         </is>
       </c>
+      <c r="V34" s="16" t="inlineStr">
+        <is>
+          <t>Hard/Soft</t>
+        </is>
+      </c>
+      <c r="W34" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X34" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y34" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z34" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA34" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB34" s="16" t="inlineStr">
+        <is>
+          <t>SCH-C</t>
+        </is>
+      </c>
+      <c r="AC34" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD34" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="76" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
@@ -5293,6 +6698,49 @@
           <t>Do we want a branch-level maximum as well as an individual one?</t>
         </is>
       </c>
+      <c r="V35" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W35" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X35" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y35" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z35" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA35" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB35" s="16" t="inlineStr">
+        <is>
+          <t>SCH-C</t>
+        </is>
+      </c>
+      <c r="AC35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="76" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
@@ -5400,6 +6848,49 @@
           <t>Can we use clinician home addresses for drive-time calculation, and has that been agreed with them?</t>
         </is>
       </c>
+      <c r="V36" s="16" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="W36" s="16" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="X36" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Y36" s="16" t="inlineStr">
+        <is>
+          <t>Manual + Routing</t>
+        </is>
+      </c>
+      <c r="Z36" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA36" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB36" s="16" t="inlineStr">
+        <is>
+          <t>SCH-D</t>
+        </is>
+      </c>
+      <c r="AC36" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD36" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="76" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
@@ -5503,6 +6994,49 @@
           <t>Nothing outstanding — this row is solid.</t>
         </is>
       </c>
+      <c r="V37" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W37" s="16" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="X37" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y37" s="16" t="inlineStr">
+        <is>
+          <t>HCHB</t>
+        </is>
+      </c>
+      <c r="Z37" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA37" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB37" s="16" t="inlineStr">
+        <is>
+          <t>SCH-A</t>
+        </is>
+      </c>
+      <c r="AC37" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD37" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="76" customHeight="1">
       <c r="A38" s="16" t="inlineStr">
@@ -5606,6 +7140,49 @@
           <t>Nothing outstanding.</t>
         </is>
       </c>
+      <c r="V38" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W38" s="16" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="X38" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y38" s="16" t="inlineStr">
+        <is>
+          <t>HCHB</t>
+        </is>
+      </c>
+      <c r="Z38" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA38" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB38" s="16" t="inlineStr">
+        <is>
+          <t>SCH-A</t>
+        </is>
+      </c>
+      <c r="AC38" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD38" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="76" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
@@ -5713,6 +7290,15 @@
           <t>Can the auth coordination note be surfaced into the plan-of-care screen, and who owns that change?</t>
         </is>
       </c>
+      <c r="V39" s="16" t="n"/>
+      <c r="W39" s="16" t="n"/>
+      <c r="X39" s="16" t="n"/>
+      <c r="Y39" s="16" t="n"/>
+      <c r="Z39" s="16" t="n"/>
+      <c r="AA39" s="16" t="n"/>
+      <c r="AB39" s="16" t="n"/>
+      <c r="AC39" s="16" t="n"/>
+      <c r="AD39" s="16" t="n"/>
     </row>
     <row r="40" ht="76" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
@@ -5820,6 +7406,15 @@
           <t>What is the current DCS add-on workflow, and is it consistent across branches?</t>
         </is>
       </c>
+      <c r="V40" s="16" t="n"/>
+      <c r="W40" s="16" t="n"/>
+      <c r="X40" s="16" t="n"/>
+      <c r="Y40" s="16" t="n"/>
+      <c r="Z40" s="16" t="n"/>
+      <c r="AA40" s="16" t="n"/>
+      <c r="AB40" s="16" t="n"/>
+      <c r="AC40" s="16" t="n"/>
+      <c r="AD40" s="16" t="n"/>
     </row>
     <row r="41" ht="76" customHeight="1">
       <c r="A41" s="16" t="inlineStr">
@@ -5923,6 +7518,49 @@
           <t>Nothing outstanding.</t>
         </is>
       </c>
+      <c r="V41" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W41" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X41" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y41" s="16" t="inlineStr">
+        <is>
+          <t>HCHB</t>
+        </is>
+      </c>
+      <c r="Z41" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA41" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB41" s="16" t="inlineStr">
+        <is>
+          <t>SCH-B</t>
+        </is>
+      </c>
+      <c r="AC41" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD41" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="76" customHeight="1">
       <c r="A42" s="16" t="inlineStr">
@@ -6030,6 +7668,49 @@
           <t>Nothing outstanding.</t>
         </is>
       </c>
+      <c r="V42" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W42" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X42" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y42" s="16" t="inlineStr">
+        <is>
+          <t>HCHB</t>
+        </is>
+      </c>
+      <c r="Z42" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA42" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB42" s="16" t="inlineStr">
+        <is>
+          <t>SCH-B</t>
+        </is>
+      </c>
+      <c r="AC42" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD42" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="76" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
@@ -6133,6 +7814,49 @@
           <t>Nothing outstanding.</t>
         </is>
       </c>
+      <c r="V43" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W43" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X43" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y43" s="16" t="inlineStr">
+        <is>
+          <t>HCHB</t>
+        </is>
+      </c>
+      <c r="Z43" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA43" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB43" s="16" t="inlineStr">
+        <is>
+          <t>SCH-B</t>
+        </is>
+      </c>
+      <c r="AC43" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD43" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="76" customHeight="1">
       <c r="A44" s="16" t="inlineStr">
@@ -6240,6 +7964,15 @@
           <t>Can queue age be reported daily, and who owns acting on it?</t>
         </is>
       </c>
+      <c r="V44" s="16" t="n"/>
+      <c r="W44" s="16" t="n"/>
+      <c r="X44" s="16" t="n"/>
+      <c r="Y44" s="16" t="n"/>
+      <c r="Z44" s="16" t="n"/>
+      <c r="AA44" s="16" t="n"/>
+      <c r="AB44" s="16" t="n"/>
+      <c r="AC44" s="16" t="n"/>
+      <c r="AD44" s="16" t="n"/>
     </row>
     <row r="45" ht="76" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
@@ -6343,6 +8076,49 @@
           <t>How far do we want to push routine visits to assistants, and who owns that decision?</t>
         </is>
       </c>
+      <c r="V45" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W45" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X45" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y45" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="Z45" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA45" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB45" s="16" t="inlineStr">
+        <is>
+          <t>SCH-E</t>
+        </is>
+      </c>
+      <c r="AC45" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD45" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="76" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
@@ -6450,6 +8226,49 @@
           <t>Would we build a competency register, and who maintains it?</t>
         </is>
       </c>
+      <c r="V46" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W46" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X46" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Y46" s="16" t="inlineStr">
+        <is>
+          <t>Workday + Manual</t>
+        </is>
+      </c>
+      <c r="Z46" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA46" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB46" s="16" t="inlineStr">
+        <is>
+          <t>SCH-E</t>
+        </is>
+      </c>
+      <c r="AC46" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD46" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="76" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
@@ -6553,6 +8372,49 @@
           <t>Do we have any usable acuity measure today, or is it entirely judgment?</t>
         </is>
       </c>
+      <c r="V47" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W47" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X47" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y47" s="16" t="inlineStr">
+        <is>
+          <t>HCHB + Manual</t>
+        </is>
+      </c>
+      <c r="Z47" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA47" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB47" s="16" t="inlineStr">
+        <is>
+          <t>SCH-E</t>
+        </is>
+      </c>
+      <c r="AC47" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD47" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="76" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
@@ -6656,6 +8518,49 @@
           <t>Where are clinician restrictions recorded today? This may be the easiest structured-data win on the sheet.</t>
         </is>
       </c>
+      <c r="V48" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W48" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X48" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y48" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z48" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA48" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB48" s="16" t="inlineStr">
+        <is>
+          <t>SCH-F</t>
+        </is>
+      </c>
+      <c r="AC48" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD48" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="76" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
@@ -6763,6 +8668,49 @@
           <t>How much continuity are we willing to trade for routing efficiency? A policy call, not a technical one.</t>
         </is>
       </c>
+      <c r="V49" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W49" s="16" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="X49" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y49" s="16" t="inlineStr">
+        <is>
+          <t>HCHB</t>
+        </is>
+      </c>
+      <c r="Z49" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA49" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB49" s="16" t="inlineStr">
+        <is>
+          <t>SCH-G</t>
+        </is>
+      </c>
+      <c r="AC49" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD49" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="76" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
@@ -6866,6 +8814,49 @@
           <t>Nothing outstanding.</t>
         </is>
       </c>
+      <c r="V50" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W50" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X50" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y50" s="16" t="inlineStr">
+        <is>
+          <t>HCHB</t>
+        </is>
+      </c>
+      <c r="Z50" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA50" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB50" s="16" t="inlineStr">
+        <is>
+          <t>SCH-L</t>
+        </is>
+      </c>
+      <c r="AC50" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD50" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="76" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
@@ -6969,6 +8960,49 @@
           <t>Could clinically driven timing be flagged distinctly from preference in the record?</t>
         </is>
       </c>
+      <c r="V51" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W51" s="16" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="X51" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y51" s="16" t="inlineStr">
+        <is>
+          <t>HCHB + Manual</t>
+        </is>
+      </c>
+      <c r="Z51" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA51" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB51" s="16" t="inlineStr">
+        <is>
+          <t>SCH-K</t>
+        </is>
+      </c>
+      <c r="AC51" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD51" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="76" customHeight="1">
       <c r="A52" s="16" t="inlineStr">
@@ -7072,6 +9106,49 @@
           <t>Are there written sequencing rules, or is this entirely clinician knowledge?</t>
         </is>
       </c>
+      <c r="V52" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W52" s="16" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="X52" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Y52" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z52" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA52" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB52" s="16" t="inlineStr">
+        <is>
+          <t>SCH-K</t>
+        </is>
+      </c>
+      <c r="AC52" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD52" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="76" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
@@ -7175,6 +9252,15 @@
           <t>Is Pulse data reachable from scheduling today, and in what form?</t>
         </is>
       </c>
+      <c r="V53" s="16" t="n"/>
+      <c r="W53" s="16" t="n"/>
+      <c r="X53" s="16" t="n"/>
+      <c r="Y53" s="16" t="n"/>
+      <c r="Z53" s="16" t="n"/>
+      <c r="AA53" s="16" t="n"/>
+      <c r="AB53" s="16" t="n"/>
+      <c r="AC53" s="16" t="n"/>
+      <c r="AD53" s="16" t="n"/>
     </row>
     <row r="54" ht="76" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
@@ -7282,6 +9368,49 @@
           <t>What routing data does HCHB actually use today — distance, or real drive time?</t>
         </is>
       </c>
+      <c r="V54" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W54" s="16" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="X54" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y54" s="16" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="Z54" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA54" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB54" s="16" t="inlineStr">
+        <is>
+          <t>SCH-D</t>
+        </is>
+      </c>
+      <c r="AC54" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD54" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="76" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
@@ -7389,6 +9518,49 @@
           <t>Is mileage currently reported anywhere the branch actually looks at?</t>
         </is>
       </c>
+      <c r="V55" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="W55" s="16" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="X55" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y55" s="16" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="Z55" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA55" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB55" s="16" t="inlineStr">
+        <is>
+          <t>SCH-D</t>
+        </is>
+      </c>
+      <c r="AC55" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD55" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="76" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
@@ -7492,6 +9664,49 @@
           <t>Nothing outstanding.</t>
         </is>
       </c>
+      <c r="V56" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W56" s="16" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="X56" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y56" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="Z56" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA56" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB56" s="16" t="inlineStr">
+        <is>
+          <t>SCH-D</t>
+        </is>
+      </c>
+      <c r="AC56" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD56" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="76" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
@@ -7599,6 +9814,49 @@
           <t>Do we want to move to committed time windows, and what would that cost in flexibility?</t>
         </is>
       </c>
+      <c r="V57" s="16" t="inlineStr">
+        <is>
+          <t>Hard/Soft</t>
+        </is>
+      </c>
+      <c r="W57" s="16" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="X57" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Y57" s="16" t="inlineStr">
+        <is>
+          <t>HCHB + Manual</t>
+        </is>
+      </c>
+      <c r="Z57" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA57" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB57" s="16" t="inlineStr">
+        <is>
+          <t>SCH-D</t>
+        </is>
+      </c>
+      <c r="AC57" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD57" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="76" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
@@ -7702,6 +9960,15 @@
           <t>Which markets have safety rules today, and where are they written down?</t>
         </is>
       </c>
+      <c r="V58" s="16" t="n"/>
+      <c r="W58" s="16" t="n"/>
+      <c r="X58" s="16" t="n"/>
+      <c r="Y58" s="16" t="n"/>
+      <c r="Z58" s="16" t="n"/>
+      <c r="AA58" s="16" t="n"/>
+      <c r="AB58" s="16" t="n"/>
+      <c r="AC58" s="16" t="n"/>
+      <c r="AD58" s="16" t="n"/>
     </row>
     <row r="59" ht="76" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
@@ -7809,6 +10076,49 @@
           <t>Is 42% by Tuesday the standard we want to hold branches to?</t>
         </is>
       </c>
+      <c r="V59" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W59" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X59" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y59" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="Z59" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA59" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB59" s="16" t="inlineStr">
+        <is>
+          <t>SCH-N</t>
+        </is>
+      </c>
+      <c r="AC59" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD59" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="76" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
@@ -7916,6 +10226,49 @@
           <t>Who should own the daily pace read — Clinical Manager, Scheduler, or both?</t>
         </is>
       </c>
+      <c r="V60" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="W60" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X60" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y60" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="Z60" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA60" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB60" s="16" t="inlineStr">
+        <is>
+          <t>SCH-N</t>
+        </is>
+      </c>
+      <c r="AC60" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD60" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="76" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
@@ -8023,6 +10376,49 @@
           <t>Nothing outstanding.</t>
         </is>
       </c>
+      <c r="V61" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W61" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X61" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y61" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="Z61" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA61" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB61" s="16" t="inlineStr">
+        <is>
+          <t>SCH-N</t>
+        </is>
+      </c>
+      <c r="AC61" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD61" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="76" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
@@ -8130,6 +10526,49 @@
           <t>Can we detect a likely miss earlier than the missed status appears?</t>
         </is>
       </c>
+      <c r="V62" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W62" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X62" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y62" s="16" t="inlineStr">
+        <is>
+          <t>HCHB + Derived</t>
+        </is>
+      </c>
+      <c r="Z62" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA62" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB62" s="16" t="inlineStr">
+        <is>
+          <t>SCH-M</t>
+        </is>
+      </c>
+      <c r="AC62" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD62" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="76" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
@@ -8233,6 +10672,49 @@
           <t>Nothing outstanding.</t>
         </is>
       </c>
+      <c r="V63" s="16" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="W63" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X63" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y63" s="16" t="inlineStr">
+        <is>
+          <t>HCHB</t>
+        </is>
+      </c>
+      <c r="Z63" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA63" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB63" s="16" t="inlineStr">
+        <is>
+          <t>SCH-M</t>
+        </is>
+      </c>
+      <c r="AC63" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD63" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="76" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
@@ -8340,6 +10822,15 @@
           <t>How long is the blind window in practice? Nobody has measured it.</t>
         </is>
       </c>
+      <c r="V64" s="16" t="n"/>
+      <c r="W64" s="16" t="n"/>
+      <c r="X64" s="16" t="n"/>
+      <c r="Y64" s="16" t="n"/>
+      <c r="Z64" s="16" t="n"/>
+      <c r="AA64" s="16" t="n"/>
+      <c r="AB64" s="16" t="n"/>
+      <c r="AC64" s="16" t="n"/>
+      <c r="AD64" s="16" t="n"/>
     </row>
     <row r="65" ht="76" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
@@ -8447,6 +10938,49 @@
           <t>Should refusals carry a review date so they do not calcify?</t>
         </is>
       </c>
+      <c r="V65" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W65" s="16" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="X65" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y65" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z65" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA65" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB65" s="16" t="inlineStr">
+        <is>
+          <t>SCH-I</t>
+        </is>
+      </c>
+      <c r="AC65" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD65" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="76" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
@@ -8554,6 +11088,49 @@
           <t>Nothing outstanding.</t>
         </is>
       </c>
+      <c r="V66" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W66" s="16" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="X66" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y66" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z66" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA66" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB66" s="16" t="inlineStr">
+        <is>
+          <t>SCH-I</t>
+        </is>
+      </c>
+      <c r="AC66" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD66" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="76" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
@@ -8657,6 +11234,49 @@
           <t>Could standing commitments be captured as structured dates rather than free text?</t>
         </is>
       </c>
+      <c r="V67" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W67" s="16" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="X67" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y67" s="16" t="inlineStr">
+        <is>
+          <t>Manual + HCHB</t>
+        </is>
+      </c>
+      <c r="Z67" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA67" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB67" s="16" t="inlineStr">
+        <is>
+          <t>SCH-I</t>
+        </is>
+      </c>
+      <c r="AC67" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD67" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="76" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
@@ -8764,6 +11384,49 @@
           <t>How often does caregiver availability change mid-episode, and does anyone update the note when it does?</t>
         </is>
       </c>
+      <c r="V68" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W68" s="16" t="inlineStr">
+        <is>
+          <t>Caregiver</t>
+        </is>
+      </c>
+      <c r="X68" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y68" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z68" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA68" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB68" s="16" t="inlineStr">
+        <is>
+          <t>SCH-J</t>
+        </is>
+      </c>
+      <c r="AC68" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD68" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="76" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
@@ -8871,6 +11534,49 @@
           <t>Nothing outstanding — but confirm the note reliably reaches the scheduler.</t>
         </is>
       </c>
+      <c r="V69" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W69" s="16" t="inlineStr">
+        <is>
+          <t>Caregiver</t>
+        </is>
+      </c>
+      <c r="X69" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y69" s="16" t="inlineStr">
+        <is>
+          <t>Manual + HCHB</t>
+        </is>
+      </c>
+      <c r="Z69" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA69" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB69" s="16" t="inlineStr">
+        <is>
+          <t>SCH-J</t>
+        </is>
+      </c>
+      <c r="AC69" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD69" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="76" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
@@ -8978,6 +11684,49 @@
           <t>Is there any value in capturing caregiver availability as structured data, or is it too volatile to be worth it?</t>
         </is>
       </c>
+      <c r="V70" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W70" s="16" t="inlineStr">
+        <is>
+          <t>Caregiver</t>
+        </is>
+      </c>
+      <c r="X70" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y70" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z70" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA70" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB70" s="16" t="inlineStr">
+        <is>
+          <t>SCH-J</t>
+        </is>
+      </c>
+      <c r="AC70" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD70" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="76" customHeight="1">
       <c r="A71" s="16" t="inlineStr">
@@ -9085,6 +11834,49 @@
           <t>Nothing outstanding.</t>
         </is>
       </c>
+      <c r="V71" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W71" s="16" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="X71" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Y71" s="16" t="inlineStr">
+        <is>
+          <t>Manual + HCHB</t>
+        </is>
+      </c>
+      <c r="Z71" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA71" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB71" s="16" t="inlineStr">
+        <is>
+          <t>SCH-K</t>
+        </is>
+      </c>
+      <c r="AC71" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD71" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="76" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
@@ -9188,6 +11980,49 @@
           <t>Is there a policy on how this is recorded and honoured?</t>
         </is>
       </c>
+      <c r="V72" s="16" t="inlineStr">
+        <is>
+          <t>Hard/Soft</t>
+        </is>
+      </c>
+      <c r="W72" s="16" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="X72" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y72" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z72" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA72" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB72" s="16" t="inlineStr">
+        <is>
+          <t>SCH-H</t>
+        </is>
+      </c>
+      <c r="AC72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="76" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
@@ -9295,6 +12130,49 @@
           <t>Do we hold clinician language capability anywhere today?</t>
         </is>
       </c>
+      <c r="V73" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W73" s="16" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="X73" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y73" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z73" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA73" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB73" s="16" t="inlineStr">
+        <is>
+          <t>SCH-H</t>
+        </is>
+      </c>
+      <c r="AC73" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD73" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="76" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
@@ -9398,6 +12276,49 @@
           <t>If outreach is automated, how do we preserve the 'is the patient really home' check?</t>
         </is>
       </c>
+      <c r="V74" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W74" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X74" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y74" s="16" t="inlineStr">
+        <is>
+          <t>Telephony + HCHB</t>
+        </is>
+      </c>
+      <c r="Z74" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA74" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB74" s="16" t="inlineStr">
+        <is>
+          <t>CRD-A</t>
+        </is>
+      </c>
+      <c r="AC74" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD74" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="76" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
@@ -9505,6 +12426,49 @@
           <t>Nothing outstanding — but this row depends on S-28 and S-30 being right.</t>
         </is>
       </c>
+      <c r="V75" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W75" s="16" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="X75" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y75" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z75" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA75" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB75" s="16" t="inlineStr">
+        <is>
+          <t>CRD-B</t>
+        </is>
+      </c>
+      <c r="AC75" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD75" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="76" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
@@ -9612,6 +12576,49 @@
           <t>How do we automate the round without losing what the conversation catches?</t>
         </is>
       </c>
+      <c r="V76" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W76" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X76" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Y76" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z76" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA76" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB76" s="16" t="inlineStr">
+        <is>
+          <t>CRD-A</t>
+        </is>
+      </c>
+      <c r="AC76" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD76" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="76" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
@@ -9715,6 +12722,49 @@
           <t>Nothing outstanding.</t>
         </is>
       </c>
+      <c r="V77" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W77" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X77" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y77" s="16" t="inlineStr">
+        <is>
+          <t>Telephony</t>
+        </is>
+      </c>
+      <c r="Z77" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA77" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB77" s="16" t="inlineStr">
+        <is>
+          <t>CRD-A</t>
+        </is>
+      </c>
+      <c r="AC77" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD77" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="76" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
@@ -9818,6 +12868,49 @@
           <t>Are we comfortable with the location tracking this implies, and have clinicians been consulted?</t>
         </is>
       </c>
+      <c r="V78" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W78" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X78" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y78" s="16" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="Z78" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA78" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AB78" s="16" t="inlineStr">
+        <is>
+          <t>CRD-A</t>
+        </is>
+      </c>
+      <c r="AC78" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD78" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="76" customHeight="1">
       <c r="A79" s="16" t="inlineStr">
@@ -9921,6 +13014,49 @@
           <t>Where would channel preference and consent live, and who captures it at admission?</t>
         </is>
       </c>
+      <c r="V79" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W79" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X79" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Y79" s="16" t="inlineStr">
+        <is>
+          <t>Manual + Config</t>
+        </is>
+      </c>
+      <c r="Z79" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA79" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB79" s="16" t="inlineStr">
+        <is>
+          <t>CRD-A</t>
+        </is>
+      </c>
+      <c r="AC79" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD79" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="76" customHeight="1">
       <c r="A80" s="16" t="inlineStr">
@@ -10028,6 +13164,15 @@
           <t>Where would POA status be captured so the scheduler sees it before booking rather than after?</t>
         </is>
       </c>
+      <c r="V80" s="16" t="n"/>
+      <c r="W80" s="16" t="n"/>
+      <c r="X80" s="16" t="n"/>
+      <c r="Y80" s="16" t="n"/>
+      <c r="Z80" s="16" t="n"/>
+      <c r="AA80" s="16" t="n"/>
+      <c r="AB80" s="16" t="n"/>
+      <c r="AC80" s="16" t="n"/>
+      <c r="AD80" s="16" t="n"/>
     </row>
     <row r="81" ht="76" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
@@ -10131,6 +13276,15 @@
           <t>Who verifies the number, and at what point in admission?</t>
         </is>
       </c>
+      <c r="V81" s="16" t="n"/>
+      <c r="W81" s="16" t="n"/>
+      <c r="X81" s="16" t="n"/>
+      <c r="Y81" s="16" t="n"/>
+      <c r="Z81" s="16" t="n"/>
+      <c r="AA81" s="16" t="n"/>
+      <c r="AB81" s="16" t="n"/>
+      <c r="AC81" s="16" t="n"/>
+      <c r="AD81" s="16" t="n"/>
     </row>
     <row r="82" ht="76" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
@@ -10234,6 +13388,15 @@
           <t>Does this change what we can promise vendors about pre-admission outreach?</t>
         </is>
       </c>
+      <c r="V82" s="16" t="n"/>
+      <c r="W82" s="16" t="n"/>
+      <c r="X82" s="16" t="n"/>
+      <c r="Y82" s="16" t="n"/>
+      <c r="Z82" s="16" t="n"/>
+      <c r="AA82" s="16" t="n"/>
+      <c r="AB82" s="16" t="n"/>
+      <c r="AC82" s="16" t="n"/>
+      <c r="AD82" s="16" t="n"/>
     </row>
     <row r="83" ht="76" customHeight="1">
       <c r="A83" s="16" t="inlineStr">
@@ -10341,6 +13504,49 @@
           <t>Which branches have rapid reschedule enabled? It changes what the office actually sees.</t>
         </is>
       </c>
+      <c r="V83" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W83" s="16" t="inlineStr">
+        <is>
+          <t>Clinician</t>
+        </is>
+      </c>
+      <c r="X83" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y83" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z83" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA83" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB83" s="16" t="inlineStr">
+        <is>
+          <t>CRD-B</t>
+        </is>
+      </c>
+      <c r="AC83" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD83" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="76" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
@@ -10448,6 +13654,49 @@
           <t>Nothing outstanding.</t>
         </is>
       </c>
+      <c r="V84" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W84" s="16" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="X84" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Y84" s="16" t="inlineStr">
+        <is>
+          <t>HCHB + Manual</t>
+        </is>
+      </c>
+      <c r="Z84" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA84" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB84" s="16" t="inlineStr">
+        <is>
+          <t>CRD-B</t>
+        </is>
+      </c>
+      <c r="AC84" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD84" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="76" customHeight="1">
       <c r="A85" s="16" t="inlineStr">
@@ -10555,6 +13804,49 @@
           <t>Would we let the system contact clinicians directly with an open visit, or must a person always make the ask?</t>
         </is>
       </c>
+      <c r="V85" s="16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="W85" s="16" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="X85" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y85" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Z85" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA85" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB85" s="16" t="inlineStr">
+        <is>
+          <t>CRD-B</t>
+        </is>
+      </c>
+      <c r="AC85" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD85" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="76" customHeight="1">
       <c r="A86" s="38" t="inlineStr">
@@ -10574,7 +13866,7 @@
       </c>
       <c r="D86" s="19" t="inlineStr">
         <is>
-          <t>When plans change</t>
+          <t>Incentives &amp; offers</t>
         </is>
       </c>
       <c r="E86" s="18" t="inlineStr">
@@ -10662,6 +13954,15 @@
           <t>Numbered 26 Aug. Confirm MVP and gating — it is asked of vendors in Part B row 10 but carries no MVP call yet.</t>
         </is>
       </c>
+      <c r="V86" s="16" t="n"/>
+      <c r="W86" s="16" t="n"/>
+      <c r="X86" s="16" t="n"/>
+      <c r="Y86" s="16" t="n"/>
+      <c r="Z86" s="16" t="n"/>
+      <c r="AA86" s="16" t="n"/>
+      <c r="AB86" s="16" t="n"/>
+      <c r="AC86" s="16" t="n"/>
+      <c r="AD86" s="16" t="n"/>
     </row>
     <row r="87" ht="76" customHeight="1">
       <c r="A87" s="16" t="inlineStr">
@@ -10769,6 +14070,49 @@
           <t>Is there a standard on how many visits a patient should have in one day?</t>
         </is>
       </c>
+      <c r="V87" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W87" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X87" s="16" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="Y87" s="16" t="inlineStr">
+        <is>
+          <t>HCHB + Manual</t>
+        </is>
+      </c>
+      <c r="Z87" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA87" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB87" s="16" t="inlineStr">
+        <is>
+          <t>CRD-C</t>
+        </is>
+      </c>
+      <c r="AC87" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD87" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="76" customHeight="1">
       <c r="A88" s="16" t="inlineStr">
@@ -10876,6 +14220,49 @@
           <t>Nothing outstanding.</t>
         </is>
       </c>
+      <c r="V88" s="16" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="W88" s="16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="X88" s="16" t="inlineStr">
+        <is>
+          <t>In-system</t>
+        </is>
+      </c>
+      <c r="Y88" s="16" t="inlineStr">
+        <is>
+          <t>HCHB</t>
+        </is>
+      </c>
+      <c r="Z88" s="16" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+      <c r="AA88" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AB88" s="16" t="inlineStr">
+        <is>
+          <t>CRD-C</t>
+        </is>
+      </c>
+      <c r="AC88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD88" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="76" customHeight="1">
       <c r="A89" s="16" t="inlineStr">
@@ -10981,6 +14368,49 @@
       <c r="U89" s="18" t="inlineStr">
         <is>
           <t>Is there an appetite to measure this directly, or should it be estimated from the automation we remove?</t>
+        </is>
+      </c>
+      <c r="V89" s="16" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="W89" s="16" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="X89" s="16" t="inlineStr">
+        <is>
+          <t>Tacit</t>
+        </is>
+      </c>
+      <c r="Y89" s="16" t="inlineStr">
+        <is>
+          <t>Derived + Manual</t>
+        </is>
+      </c>
+      <c r="Z89" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative</t>
+        </is>
+      </c>
+      <c r="AA89" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AB89" s="16" t="inlineStr">
+        <is>
+          <t>CRD-D</t>
+        </is>
+      </c>
+      <c r="AC89" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD89" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -11082,6 +14512,15 @@
           <t>Confirm MVP, gating and posture. Do we capture a structured reason code, and is that a hard ask of the vendor or a phase-two ambition?</t>
         </is>
       </c>
+      <c r="V90" s="16" t="n"/>
+      <c r="W90" s="16" t="n"/>
+      <c r="X90" s="16" t="n"/>
+      <c r="Y90" s="16" t="n"/>
+      <c r="Z90" s="16" t="n"/>
+      <c r="AA90" s="16" t="n"/>
+      <c r="AB90" s="16" t="n"/>
+      <c r="AC90" s="16" t="n"/>
+      <c r="AD90" s="16" t="n"/>
     </row>
     <row r="91" ht="76" customHeight="1">
       <c r="A91" s="38" t="inlineStr">
@@ -11181,6 +14620,15 @@
           <t>Confirm MVP, gating and posture. This needs a scheduler and clinician session before it can be specified properly.</t>
         </is>
       </c>
+      <c r="V91" s="16" t="n"/>
+      <c r="W91" s="16" t="n"/>
+      <c r="X91" s="16" t="n"/>
+      <c r="Y91" s="16" t="n"/>
+      <c r="Z91" s="16" t="n"/>
+      <c r="AA91" s="16" t="n"/>
+      <c r="AB91" s="16" t="n"/>
+      <c r="AC91" s="16" t="n"/>
+      <c r="AD91" s="16" t="n"/>
     </row>
     <row r="92" ht="76" customHeight="1">
       <c r="A92" s="38" t="inlineStr">
@@ -11276,6 +14724,15 @@
           <t>Is this a territory attribute or a routing penalty? The placement decides the layer. Also depends on the drive-time data source decision still open on S-17.</t>
         </is>
       </c>
+      <c r="V92" s="16" t="n"/>
+      <c r="W92" s="16" t="n"/>
+      <c r="X92" s="16" t="n"/>
+      <c r="Y92" s="16" t="n"/>
+      <c r="Z92" s="16" t="n"/>
+      <c r="AA92" s="16" t="n"/>
+      <c r="AB92" s="16" t="n"/>
+      <c r="AC92" s="16" t="n"/>
+      <c r="AD92" s="16" t="n"/>
     </row>
     <row r="93" ht="76" customHeight="1">
       <c r="A93" s="38" t="inlineStr">
@@ -11371,6 +14828,15 @@
           <t>Confirm MVP, gating and posture. Pairs with S-51 — the accept/decline loop is where a hand-off would actually happen.</t>
         </is>
       </c>
+      <c r="V93" s="16" t="n"/>
+      <c r="W93" s="16" t="n"/>
+      <c r="X93" s="16" t="n"/>
+      <c r="Y93" s="16" t="n"/>
+      <c r="Z93" s="16" t="n"/>
+      <c r="AA93" s="16" t="n"/>
+      <c r="AB93" s="16" t="n"/>
+      <c r="AC93" s="16" t="n"/>
+      <c r="AD93" s="16" t="n"/>
     </row>
     <row r="94" ht="76" customHeight="1">
       <c r="A94" s="38" t="inlineStr">
@@ -11390,7 +14856,7 @@
       </c>
       <c r="D94" s="19" t="inlineStr">
         <is>
-          <t>When plans change</t>
+          <t>Incentives &amp; offers</t>
         </is>
       </c>
       <c r="E94" s="18" t="inlineStr">
@@ -11470,6 +14936,15 @@
           <t>Confirm MVP, gating and posture. This is an incentive-policy decision as much as a product one, and it overlaps CO-15 — decide whether they are one row or two.</t>
         </is>
       </c>
+      <c r="V94" s="16" t="n"/>
+      <c r="W94" s="16" t="n"/>
+      <c r="X94" s="16" t="n"/>
+      <c r="Y94" s="16" t="n"/>
+      <c r="Z94" s="16" t="n"/>
+      <c r="AA94" s="16" t="n"/>
+      <c r="AB94" s="16" t="n"/>
+      <c r="AC94" s="16" t="n"/>
+      <c r="AD94" s="16" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:U89"/>

--- a/agents/compassus-capacity-pm/variables/CapacitySchedulingVariableWorkbook.xlsx
+++ b/agents/compassus-capacity-pm/variables/CapacitySchedulingVariableWorkbook.xlsx
@@ -1583,7 +1583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD94"/>
+  <dimension ref="A1:AE94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1616,6 +1616,7 @@
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="20" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1769,6 +1770,11 @@
           <t>Conflict risk (8.13)</t>
         </is>
       </c>
+      <c r="AE1" s="15" t="inlineStr">
+        <is>
+          <t>Automation posture (8.13)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="76" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
@@ -1919,6 +1925,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE2" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="76" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
@@ -2069,6 +2080,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE3" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="76" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
@@ -2219,6 +2235,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE4" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="76" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
@@ -2365,6 +2386,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="AE5" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="76" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
@@ -2511,6 +2537,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="AE6" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="76" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
@@ -2661,6 +2692,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE7" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="76" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
@@ -2811,6 +2847,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE8" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
@@ -2957,6 +2998,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE9" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="76" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
@@ -3107,6 +3153,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE10" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="76" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
@@ -3257,6 +3308,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE11" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="76" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
@@ -3407,6 +3463,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE12" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="76" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
@@ -3557,6 +3618,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE13" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="76" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
@@ -3707,6 +3773,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="AE14" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="76" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
@@ -3853,6 +3924,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE15" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="76" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
@@ -4003,6 +4079,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="AE16" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="76" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
@@ -4147,6 +4228,11 @@
       <c r="AD17" s="16" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="AE17" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
         </is>
       </c>
     </row>
@@ -4265,6 +4351,7 @@
       <c r="AB18" s="16" t="n"/>
       <c r="AC18" s="16" t="n"/>
       <c r="AD18" s="16" t="n"/>
+      <c r="AE18" s="16" t="n"/>
     </row>
     <row r="19" ht="76" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
@@ -4381,6 +4468,7 @@
       <c r="AB19" s="16" t="n"/>
       <c r="AC19" s="16" t="n"/>
       <c r="AD19" s="16" t="n"/>
+      <c r="AE19" s="16" t="n"/>
     </row>
     <row r="20" ht="76" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
@@ -4531,6 +4619,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE20" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="76" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
@@ -4681,6 +4774,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="AE21" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="76" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
@@ -4827,6 +4925,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE22" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="76" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
@@ -4977,6 +5080,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="AE23" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="76" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
@@ -5127,6 +5235,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="AE24" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="76" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
@@ -5273,6 +5386,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="AE25" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="76" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
@@ -5423,6 +5541,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE26" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="76" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
@@ -5569,6 +5692,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE27" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="76" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
@@ -5719,6 +5847,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE28" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="76" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
@@ -5865,6 +5998,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE29" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="76" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
@@ -6011,6 +6149,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE30" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="76" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
@@ -6157,6 +6300,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE31" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="76" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
@@ -6303,6 +6451,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE32" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="76" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
@@ -6449,6 +6602,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE33" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="76" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
@@ -6595,6 +6753,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE34" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="76" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
@@ -6741,6 +6904,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="AE35" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="76" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
@@ -6891,6 +7059,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE36" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="76" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
@@ -7037,6 +7210,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE37" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="76" customHeight="1">
       <c r="A38" s="16" t="inlineStr">
@@ -7181,6 +7359,11 @@
       <c r="AD38" s="16" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="AE38" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
         </is>
       </c>
     </row>
@@ -7299,6 +7482,7 @@
       <c r="AB39" s="16" t="n"/>
       <c r="AC39" s="16" t="n"/>
       <c r="AD39" s="16" t="n"/>
+      <c r="AE39" s="16" t="n"/>
     </row>
     <row r="40" ht="76" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
@@ -7415,6 +7599,7 @@
       <c r="AB40" s="16" t="n"/>
       <c r="AC40" s="16" t="n"/>
       <c r="AD40" s="16" t="n"/>
+      <c r="AE40" s="16" t="n"/>
     </row>
     <row r="41" ht="76" customHeight="1">
       <c r="A41" s="16" t="inlineStr">
@@ -7561,6 +7746,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE41" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="76" customHeight="1">
       <c r="A42" s="16" t="inlineStr">
@@ -7711,6 +7901,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE42" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="76" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
@@ -7855,6 +8050,11 @@
       <c r="AD43" s="16" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="AE43" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
         </is>
       </c>
     </row>
@@ -7973,6 +8173,7 @@
       <c r="AB44" s="16" t="n"/>
       <c r="AC44" s="16" t="n"/>
       <c r="AD44" s="16" t="n"/>
+      <c r="AE44" s="16" t="n"/>
     </row>
     <row r="45" ht="76" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
@@ -8119,6 +8320,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE45" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="76" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
@@ -8269,6 +8475,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE46" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="76" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
@@ -8415,6 +8626,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE47" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="76" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
@@ -8561,6 +8777,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE48" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="76" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
@@ -8711,6 +8932,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE49" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="76" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
@@ -8857,6 +9083,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE50" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="76" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
@@ -9003,6 +9234,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE51" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="76" customHeight="1">
       <c r="A52" s="16" t="inlineStr">
@@ -9147,6 +9383,11 @@
       <c r="AD52" s="16" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="AE52" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
         </is>
       </c>
     </row>
@@ -9261,6 +9502,7 @@
       <c r="AB53" s="16" t="n"/>
       <c r="AC53" s="16" t="n"/>
       <c r="AD53" s="16" t="n"/>
+      <c r="AE53" s="16" t="n"/>
     </row>
     <row r="54" ht="76" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
@@ -9411,6 +9653,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="AE54" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="76" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
@@ -9561,6 +9808,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE55" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="76" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
@@ -9707,6 +9959,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE56" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="76" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
@@ -9855,6 +10112,11 @@
       <c r="AD57" s="16" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="AE57" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
         </is>
       </c>
     </row>
@@ -9969,6 +10231,7 @@
       <c r="AB58" s="16" t="n"/>
       <c r="AC58" s="16" t="n"/>
       <c r="AD58" s="16" t="n"/>
+      <c r="AE58" s="16" t="n"/>
     </row>
     <row r="59" ht="76" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
@@ -10119,6 +10382,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="AE59" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="76" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
@@ -10269,6 +10537,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE60" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="76" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
@@ -10419,6 +10692,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE61" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="76" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
@@ -10569,6 +10847,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE62" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="76" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
@@ -10713,6 +10996,11 @@
       <c r="AD63" s="16" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="AE63" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
         </is>
       </c>
     </row>
@@ -10831,6 +11119,7 @@
       <c r="AB64" s="16" t="n"/>
       <c r="AC64" s="16" t="n"/>
       <c r="AD64" s="16" t="n"/>
+      <c r="AE64" s="16" t="n"/>
     </row>
     <row r="65" ht="76" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
@@ -10981,6 +11270,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE65" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="76" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
@@ -11131,6 +11425,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE66" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="76" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
@@ -11277,6 +11576,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE67" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="76" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
@@ -11427,6 +11731,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE68" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="76" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
@@ -11577,6 +11886,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE69" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="76" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
@@ -11727,6 +12041,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE70" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="76" customHeight="1">
       <c r="A71" s="16" t="inlineStr">
@@ -11877,6 +12196,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE71" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="76" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
@@ -12023,6 +12347,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE72" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="76" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
@@ -12173,6 +12502,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE73" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="76" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
@@ -12319,6 +12653,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE74" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="76" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
@@ -12469,6 +12808,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE75" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="76" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
@@ -12619,6 +12963,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE76" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="76" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
@@ -12765,6 +13114,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="AE77" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="76" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
@@ -12911,6 +13265,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE78" s="16" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="76" customHeight="1">
       <c r="A79" s="16" t="inlineStr">
@@ -13055,6 +13414,11 @@
       <c r="AD79" s="16" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="AE79" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
         </is>
       </c>
     </row>
@@ -13173,6 +13537,7 @@
       <c r="AB80" s="16" t="n"/>
       <c r="AC80" s="16" t="n"/>
       <c r="AD80" s="16" t="n"/>
+      <c r="AE80" s="16" t="n"/>
     </row>
     <row r="81" ht="76" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
@@ -13285,6 +13650,7 @@
       <c r="AB81" s="16" t="n"/>
       <c r="AC81" s="16" t="n"/>
       <c r="AD81" s="16" t="n"/>
+      <c r="AE81" s="16" t="n"/>
     </row>
     <row r="82" ht="76" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
@@ -13397,6 +13763,7 @@
       <c r="AB82" s="16" t="n"/>
       <c r="AC82" s="16" t="n"/>
       <c r="AD82" s="16" t="n"/>
+      <c r="AE82" s="16" t="n"/>
     </row>
     <row r="83" ht="76" customHeight="1">
       <c r="A83" s="16" t="inlineStr">
@@ -13547,6 +13914,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE83" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="76" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
@@ -13697,6 +14069,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE84" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="76" customHeight="1">
       <c r="A85" s="16" t="inlineStr">
@@ -13845,6 +14222,11 @@
       <c r="AD85" s="16" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="AE85" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
         </is>
       </c>
     </row>
@@ -13963,6 +14345,7 @@
       <c r="AB86" s="16" t="n"/>
       <c r="AC86" s="16" t="n"/>
       <c r="AD86" s="16" t="n"/>
+      <c r="AE86" s="16" t="n"/>
     </row>
     <row r="87" ht="76" customHeight="1">
       <c r="A87" s="16" t="inlineStr">
@@ -14113,6 +14496,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE87" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="76" customHeight="1">
       <c r="A88" s="16" t="inlineStr">
@@ -14263,6 +14651,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE88" s="16" t="inlineStr">
+        <is>
+          <t>Assist</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="76" customHeight="1">
       <c r="A89" s="16" t="inlineStr">
@@ -14411,6 +14804,11 @@
       <c r="AD89" s="16" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="AE89" s="16" t="inlineStr">
+        <is>
+          <t>Read</t>
         </is>
       </c>
     </row>
@@ -14521,6 +14919,7 @@
       <c r="AB90" s="16" t="n"/>
       <c r="AC90" s="16" t="n"/>
       <c r="AD90" s="16" t="n"/>
+      <c r="AE90" s="16" t="n"/>
     </row>
     <row r="91" ht="76" customHeight="1">
       <c r="A91" s="38" t="inlineStr">
@@ -14629,6 +15028,7 @@
       <c r="AB91" s="16" t="n"/>
       <c r="AC91" s="16" t="n"/>
       <c r="AD91" s="16" t="n"/>
+      <c r="AE91" s="16" t="n"/>
     </row>
     <row r="92" ht="76" customHeight="1">
       <c r="A92" s="38" t="inlineStr">
@@ -14733,6 +15133,7 @@
       <c r="AB92" s="16" t="n"/>
       <c r="AC92" s="16" t="n"/>
       <c r="AD92" s="16" t="n"/>
+      <c r="AE92" s="16" t="n"/>
     </row>
     <row r="93" ht="76" customHeight="1">
       <c r="A93" s="38" t="inlineStr">
@@ -14837,6 +15238,7 @@
       <c r="AB93" s="16" t="n"/>
       <c r="AC93" s="16" t="n"/>
       <c r="AD93" s="16" t="n"/>
+      <c r="AE93" s="16" t="n"/>
     </row>
     <row r="94" ht="76" customHeight="1">
       <c r="A94" s="38" t="inlineStr">
@@ -14945,6 +15347,7 @@
       <c r="AB94" s="16" t="n"/>
       <c r="AC94" s="16" t="n"/>
       <c r="AD94" s="16" t="n"/>
+      <c r="AE94" s="16" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:U89"/>
